--- a/data/vendor-search/results_all_fans.xlsx
+++ b/data/vendor-search/results_all_fans.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>7.4</v>
       </c>
-      <c r="E2" t="n">
-        <v>3.1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:o:atomberg:erica_smart_fan_firmware:1.0.36:*:*:*:*:*:*:*|cpe:2.3:h:atomberg:erica_smart_fan:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>smart fan</t>
         </is>
       </c>
     </row>
